--- a/TESTS/zlit_5_alisa.xlsx
+++ b/TESTS/zlit_5_alisa.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Льюїс Керролл — псевдонім британського математика і письменника Чарльза Лютвіджа Доджсона</t>
+          <t>Льюїс Керролл</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Чарльз Лютвідж Доджсон — Льюїс Керролл це літературний псевдонім</t>
+          <t>Чарльз Лютвідж Доджсон</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -687,6 +702,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Побігла за Білим Кроликом і провалилась у кролячу нору — і опинилась у дивовижному світі</t>
+          <t>Побігла за Білим Кроликом і провалилась у кролячу нору</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Він дивився на кишенькового годинника і казав «Я запізнююсь» — це надзвичайно зацікавило Алісу</t>
+          <t>Він дивився на кишенькового годинника і казав «Я запізнююсь»</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Вона довго летіла вниз і приземлилась у дивовижній залі з безліччю дверей — початок пригод</t>
+          <t>Вона довго летіла вниз і приземлилась у дивовижній залі з безліччю дверей</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Вона то збільшувалась то зменшувалась — їжа і напої мінювали її розміри непередбачувано</t>
+          <t>Вона то збільшувалась то зменшувалась</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Вона символізує труднощі пристосування до нового незрозумілого світу — як дитина у світі дорослих правил</t>
+          <t>Вона символізує труднощі пристосування до нового незрозумілого світу</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Всі правила — абсурдні і нелогічні: вирок до суду суд без злочину правила без смислу</t>
+          <t>Всі правила</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чому в Капелюшника, за його словами, назавжди зупинився час і завжди шість годин?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Час «образився» на нього і зупинився</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Він зламав годинник</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Він загубив годинник</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Це наказ Королеви</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>А</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>З ким Капелюшник п'є чай за нескінченним столом?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>З Мартівським Зайцем і Сонею</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>З Білим Кроликом і Грифоном</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>З Чеширським Котом і Гусеницею</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>З Валетом і Королем</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>А</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Як пересідають за столом учасники Шаленого чаювання?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Постійно пересуваються на одне місце, коли посуд забруднюється</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Сидять на одному місці</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Міняються місцями раз на рік</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Сидять по черзі зі сном</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>А</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Яке питання поставила Алісі Гусениця, сидячи на грибі?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>«Куди ти йдеш?»</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>«Скільки тобі років?»</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>«Хто ти така?»</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>«Звідки ти?»</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>В</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що порадила Гусениця Алісі для зміни розміру?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Випити з флакончика</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Знайти чарівну паличку</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Відкусити різні боки грибка</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Зачекати, поки минеться</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>В</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Яким стає Гусениця наприкінці своєї появи в історії?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишається гусеницею</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зникає назавжди</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Перетворюється на метелика</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Стає Чеширським Котом</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>В</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Що Аліса використовувала як молоток для крокету за наказом Королеви?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Звичайний дерев'яний молоток</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Живого фламінго</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Парасольку</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ракетку</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Що використовували замість крокетних м'ячів?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Камені</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Їжаків, згорнутих у клубок</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Яблука</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Капелюхи</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Яку фразу часто повторювала Королева Червів під час гри?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>«Чудовий день!»</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>«Відрубати голову!»</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>«Грай чесно!»</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>«Я виграла!»</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>У чому звинувачували Валета Червів на суді?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У втечі з в'язниці</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>В образі Короля</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У спізненні</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>У крадіжці тартів Королеви</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Г</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Кого Король призначив головою суду?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Білого Кролика</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чеширського Кота</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Капелюшника</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Самого себе як Короля</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Г</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що сталося наприкінці суду, коли Аліса почала рости?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Суд продовжився як завжди</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Аліса вибачилась і пішла</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Суд відклали</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>Аліса випадково перекинула скриню з присяжними</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>Г</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що сталося з Алісою після того, як вона випила напій з флакончика «Випий мене»?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Вона значно зменшилась</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Вона заснула</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Вона стала невидимою</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Вона почала літати</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>А</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що сталося з Алісою після того, як вона з'їла пиріжок із написом «З'їж мене»?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Вона почала рости і стала величезною</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Вона зменшилась ще більше</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Нічого не сталося</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Вона заснула</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>А</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Чому несподівані зміни розміру лякали й бентежили Алісу?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Вона не могла зрозуміти, хто вона тепер така і чи влізе у двері</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Вона боялась темряви</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Вона боялась Кролика</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Вона не любила їсти</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>А</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Б</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>На кого перетворилася дитина Герцогині, яку тримала Аліса?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>На кота</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>На жабу</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>На порося</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>На пташку</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>В</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Що постійно робила куховарка на кухні Герцогині?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Співала пісні</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Танцювала</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Кидала каструлями і додавала багато перцю в суп</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Спала</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>В</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Хто зі слізьми розповідав Алісі про своє шкільне життя «в морі»?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Грифон</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Капелюшник</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Якобина Черепаха</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Гусениця</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>В</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Як закінчилися пригоди Аліси у Країні Див?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона назавжди залишилась там</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Вона прокинулась і зрозуміла, що це був сон</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Її забрала Королева</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Вона перетворилась на карту</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Хто був поруч з Алісою, коли вона прокинулась?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Білий Кролик</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Її сестра</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Чеширський Кіт</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Капелюшник</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Як сестра Аліси поставилась до її розповіді про дивовижний сон?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Розсердилась</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Замислилась і теж почала уявляти ці чудові пригоди</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Не слухала</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Сказала, що це маячня</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>Б</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>В</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що символізує Країна Див у книзі?</t>
+          <t>Країна Див символізує дивний дорослий світ із незрозумілими для дитини правилами.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яка роль нонсенсу і абсурду в книзі Керролла?</t>
+          <t>Нонсенс і абсурдні діалоги в книзі Керролла використані лише для сміху і не мають жодного смислу.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Чому «Аліса в Країні Див» є не лише дитячою книгою?</t>
+          <t>«Аліса в Країні Див» цікава лише дітям і не містить прихованих смислів для дорослих читачів.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яка Королева Черв — і чим вона відома?</t>
+          <t>Королева Червів у книзі постійно кричить «Відрубати голову!», хоча насправді нікого не страчують.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Як закінчуються пригоди Аліси у Країні Див?</t>
+          <t>Пригоди Аліси у Країні Див закінчуються тим, що вона прокидається і розуміє, що це був сон.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Аліси в Країні Див»?</t>
+          <t>Головна ідея «Аліси в Країні Див» — показати, що дорослі правила й логіка завжди розумні та послідовні.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які дивовижні персонажі зустріла Аліса у Країні Див?</t>
+          <t>Які предмети відігравали важливу роль у пригодах Аліси?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Чеширський Кіт</t>
+          <t>Кишеньковий годинник Білого Кролика</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Капелюшник</t>
+          <t>Флакончик з написом «Випий мене»</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Мудрий Дід</t>
+          <t>Чарівна лампа</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Королева Черв</t>
+          <t>Грибок, що змінював розмір</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Таємничий кіт що вміє зникати залишаючи лише свою усмішку — мудрий але загадковий</t>
+          <t>Таємничий кіт що вміє зникати залишаючи лише свою усмішку</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>«Якщо не знаєш куди йдеш будь-яка дорога туди веде» — абсурдна але глибока відповідь на питання про напрямок</t>
+          <t>«Якщо не знаєш куди йдеш будь-яка дорога туди веде»</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Персонаж що застряг у вічному Чаюванні — годинник зупинився о шостій і час для нього не рухається</t>
+          <t>Персонаж що застряг у вічному Чаюванні</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
